--- a/QCM3_4_PHY.xlsx
+++ b/QCM3_4_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19BEB07-B139-46A0-8E77-E7C12B0ABEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6883940E-C553-4021-AF13-192B5DDD6333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="149">
   <si>
     <t>Question</t>
   </si>
@@ -72,9 +72,6 @@
     <t>$u_{AB} + u_{BK} + u_{AK} = 0$</t>
   </si>
   <si>
-    <t>$u_{HA} + u_{KB} + u_{KA} = 0$</t>
-  </si>
-  <si>
     <t>$i(t) = -\frac{dq}{dt}$</t>
   </si>
   <si>
@@ -132,9 +129,6 @@
     <t>$T = 2\pi\sqrt{LC}$</t>
   </si>
   <si>
-    <t>$T = 2\pi(LC)^{-1/2}$</t>
-  </si>
-  <si>
     <t>$T = \frac{2\pi}{\sqrt{LC}}$</t>
   </si>
   <si>
@@ -159,15 +153,6 @@
     <t>$u(t) = U_m \cos((LC)^{1/2} t + \varphi)$</t>
   </si>
   <si>
-    <t>$u(t) = U_0 e^{-t/RC}$</t>
-  </si>
-  <si>
-    <t>$u(t) = U_0$</t>
-  </si>
-  <si>
-    <t>$u(t) = 12 \cos(100t + \varphi)$</t>
-  </si>
-  <si>
     <t>$u(t) = 12 \cos(1000t)$</t>
   </si>
   <si>
@@ -306,12 +291,6 @@
     <t>On a l'équation différentielle (R et r sont strictement positifs) :</t>
   </si>
   <si>
-    <t>On obtient le graphe suivant pour la tension aux bornes du condensateur. La pseudo-période vaut :</t>
-  </si>
-  <si>
-    <t>On suppose pour cette question que $R = r = 0$. Le régime est pseudopériodique d'oscillations amorties avec une pseudo-période propre de :</t>
-  </si>
-  <si>
     <t>La tension aux bornes du condensateur s'écrit :</t>
   </si>
   <si>
@@ -331,9 +310,6 @@
   </si>
   <si>
     <t>Le signal peut se mettre sous la forme $V(t) = V_0 \sin(\omega t + \varphi)$ avec :</t>
-  </si>
-  <si>
-    <t>L'origine des dates est :</t>
   </si>
   <si>
     <t>L'amplitude est :</t>
@@ -358,10 +334,6 @@
 On étudie la décharge d'un condensateur à travers une bobine et une résistance. La bobine a une inductance L et une résistance r. On a de plus une résistance R et on note C la capacité du condensateur. Le condensateur a été préalablement chargé et à l'instant $t = 0$ on ferme l'interrupteur K.</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Dipôle LC : &lt;/b&gt;&lt;/center&gt;
-La résistance de l'inductance est négligeable ; $L = 20\text{ mH}$ et le condensateur a une capacité $C = 50\text{ \mu F}$. Le condensateur a été préalablement chargé ; on ferme l'interrupteur K à l'instant $t = 0$ et on note $q(t)$ la charge de l'armature A. A $t = 0$ la charge est positive et $U_{AB} = u_0 = 12\text{ V}$.</t>
-  </si>
-  <si>
     <t>$E = \frac{C q^2}{2} + L \frac{i^2}{2}$</t>
   </si>
   <si>
@@ -386,16 +358,10 @@
     <t>$E = \frac{1}{2} C u^2 + \frac{1}{2} L^2 C^2 \left(\frac{du}{dt}\right)^2$</t>
   </si>
   <si>
-    <t>$C \frac{d^2u}{dt^2} + u = 0$</t>
-  </si>
-  <si>
     <t>$L C \frac{du}{dt} + \frac{1}{2} u \frac{du}{dt} = 0$</t>
   </si>
   <si>
     <t>$L C \frac{du}{dt} + u = 0$</t>
-  </si>
-  <si>
-    <t>$L C \frac{d^2u}{dt^2} + u = 0$</t>
   </si>
   <si>
     <t>L'énergie totale à l'instant t vaut :</t>
@@ -414,64 +380,112 @@
  En abscisse, le temps est mesuré en dixièmes de secondes et en ordonnée la tension est en volts.</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Dipôle LC : &lt;/b&gt;&lt;/center&gt;
-Le circuit ci-contre est constitué d'une source de tension $E$, d'une inductance de valeur $L = 0,1\text{ H}$, d'un conducteur ohmique de résistance $R = 100\ \Omega$, d'un condensateur de capacité $C = 100\text{ nF}$ et d'un interrupteur K. Dans un premier temps, le régime permanent est établi dans le circuit RL et l'intensité du courant est égale à $I = 100\text{ mA}$.</t>
+    <t>PHY_QCM3_4_Q1.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM3_4_Q2.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM3_4_Q3.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM3_4_Q4.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM3_4_Q5.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM3_4_Q6.png</t>
+  </si>
+  <si>
+    <t>$\varphi = \frac{\pi}{6}$</t>
+  </si>
+  <si>
+    <t>$\varphi = \frac{\pi}{3}$</t>
+  </si>
+  <si>
+    <t>$\varphi = \frac{\pi}{2}$</t>
+  </si>
+  <si>
+    <t>$E_m = 2\cdot 10^{-4}\text{ J}$</t>
+  </si>
+  <si>
+    <t>$E_m = 2\cdot 10^{-5}\text{ J}$</t>
+  </si>
+  <si>
+    <t>$E_m = 5\cdot 10^{-5}\text{ J}$</t>
+  </si>
+  <si>
+    <t>$u_{BA} + u_{KB} + u_{KA} = 0$</t>
+  </si>
+  <si>
+    <t>$u_{AB} = (R + r).i$</t>
+  </si>
+  <si>
+    <t>$u_{AB} = -(R + r).i$</t>
+  </si>
+  <si>
+    <t>On obtient le graphe suivant pour la tension aux bornes du condensateur. 
+&lt;br&gt; En abscisses, le temps est mesuré en secondes. Il s'agit d'un régime pseudopériodique.
+&lt;br&gt;La pseudo-période vaut :</t>
+  </si>
+  <si>
+    <t>On suppose pour cette question que $R = r = 0$. 
+&lt;br&gt;Le régime est pseudopériodique d'oscillations amorties avec une pseudo-période propre de :</t>
+  </si>
+  <si>
+    <t>$T = 2\pi(LC)^{1/2}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Dipôle LC : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+La résistance de l'inductance est négligeable ; $L = 20\text{ mH}$ et le condensateur a une capacité $C = 50 \mu F$. 
+&lt;br&gt;Le condensateur a été préalablement chargé ; on ferme l'interrupteur K à l'instant $t = 0$ et on note $q(t)$ la charge de l'armature A. 
+A $t = 0$ la charge est positive et $U_{AB} = u_0 = 12\text{ V}$.</t>
+  </si>
+  <si>
+    <t>$LC \frac{d^2u}{dt^2} + u = 0$</t>
+  </si>
+  <si>
+    <t>$\frac{L}{C} \frac{d^2u}{dt^2} + u = 0$</t>
+  </si>
+  <si>
+    <t>$u(t) = U_m e^{-t/LC}$</t>
+  </si>
+  <si>
+    <t>$u(t) = U_m$</t>
+  </si>
+  <si>
+    <t>$u(t) = 12 \cos(100t + \frac{\PI}{2})$</t>
+  </si>
+  <si>
+    <t>La phase à l'origine des dates est :</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Dipôle LC : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+Le circuit ci-contre est constitué d'une source de tension $E$, d'une inductance de valeur $L = 0,1\text{ H}$, d'un conducteur ohmique de résistance $R = 100\ \Omega$, d'un condensateur de capacité $C = 100\text{ nF}$ et d'un interrupteur K. 
+&lt;br&gt;Dans un premier temps, le régime permanent est établi dans le circuit RL et l'intensité du courant est égale à $I = 100\text{ mA}$.</t>
   </si>
   <si>
     <t>Dans un deuxième temps, le condensateur étant déchargé, on bascule l'interrupteur en position 2. Il s'établit dans le circuit LC un régime sinusoïdal.
-À $t = 0^+$, juste après la fermeture de K, la tension aux bornes du condensateur est :</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Circuit RLC série : &lt;/b&gt;&lt;/center&gt;
-L'étude d'un circuit RLC série est effectué avec un oscilloscope numérique qui permet de suivre l'évolution de la tension $u_C$ aux bornes d'un condensateur et de l'intensité du courant dans le circuit. L'interrupteur K est d'abord placé en position 1 : le condensateur de capacité $C = 10^{-6}\text{ F}$ se charge grâce à la source de tension de f.é.m. $E = 3\text{ V}$. A l'instant $t = 0$, l'interrupteur est basculé en position 2 et simultanément on lance l'acquisition. $\pi^2 = 10$.</t>
-  </si>
-  <si>
-    <t>PHY_QCM3_4_Q1.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM3_4_Q2.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM3_4_Q3.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM3_4_Q4.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM3_4_Q5.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM3_4_Q6.png</t>
-  </si>
-  <si>
-    <t>$\varphi = \frac{\pi}{6}$</t>
-  </si>
-  <si>
-    <t>$\varphi = \frac{\pi}{3}$</t>
-  </si>
-  <si>
-    <t>$\varphi = \frac{\pi}{2}$</t>
-  </si>
-  <si>
-    <t>$E_m = 2\cdot 10^{-4}\text{ J}$</t>
-  </si>
-  <si>
-    <t>$E_m = 2\cdot 10^{-5}\text{ J}$</t>
-  </si>
-  <si>
-    <t>$E_m = 5\cdot 10^{-5}\text{ J}$</t>
-  </si>
-  <si>
-    <t>$u_BM = 0 V$</t>
-  </si>
-  <si>
-    <t>$u_BM = 1 V$</t>
-  </si>
-  <si>
-    <t>$u_BM = 2 V$</t>
-  </si>
-  <si>
-    <t>$u_BM = 3 V$</t>
+&lt;br&gt;À $t = 0^+$, juste après la fermeture de K, la tension aux bornes du condensateur est :</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Circuit RLC série : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+L'étude d'un circuit RLC série est effectué avec un oscilloscope numérique qui permet de suivre l'évolution de la tension $u_C$ aux bornes d'un condensateur et de l'intensité du courant dans le circuit. L'interrupteur K est d'abord placé en position 1 : le condensateur de capacité $C = 10^{-8}\text{ F}$ se charge grâce à la source de tension de f.é.m. $E = 3\text{ V}$. 
+&lt;br&gt;A l'instant $t = 0$, l'interrupteur est basculé en position 2 et simultanément on lance l'acquisition. 
+$\pi^2 = 10$.</t>
+  </si>
+  <si>
+    <t>$u_{BM} = 0 V$</t>
+  </si>
+  <si>
+    <t>$u_{BM} = 1 V$</t>
+  </si>
+  <si>
+    <t>$u_{BM} = 2 V$</t>
+  </si>
+  <si>
+    <t>$u_{BM} = 3 V$</t>
   </si>
 </sst>
 </file>
@@ -996,10 +1010,10 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>3</v>
@@ -1014,40 +1028,40 @@
         <v>14</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
         <v>12</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="K2" s="5"/>
     </row>
     <row r="3" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>
       <c r="B3" s="7" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="5"/>
@@ -1055,22 +1069,26 @@
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
       <c r="B4" s="7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="F4" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>131</v>
+      </c>
       <c r="H4" s="7"/>
       <c r="I4" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="5"/>
@@ -1078,26 +1096,26 @@
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
       <c r="B5" s="7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="5"/>
@@ -1105,82 +1123,82 @@
     <row r="6" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
       <c r="B6" s="7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>29</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="B7" s="7" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>32</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>33</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="K7" s="5"/>
     </row>
-    <row r="8" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A8" s="11"/>
       <c r="B8" s="7" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="G8" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -1188,84 +1206,84 @@
     <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
       <c r="B9" s="7" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="G9" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:11" ht="102" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="K10" s="5"/>
     </row>
     <row r="11" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="7" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="7" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -1273,26 +1291,26 @@
     <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
       <c r="B12" s="7" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="7" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
@@ -1300,26 +1318,26 @@
     <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
       <c r="B13" s="9" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>45</v>
+        <v>139</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
@@ -1327,24 +1345,26 @@
     <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="11"/>
       <c r="B14" s="7" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="7"/>
+        <v>43</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>35</v>
+      </c>
       <c r="H14" s="7"/>
       <c r="I14" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
@@ -1352,84 +1372,84 @@
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="11"/>
       <c r="B15" s="7" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
     </row>
     <row r="16" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H16" s="9"/>
       <c r="I16" s="9" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="K16" s="5"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="11"/>
       <c r="B17" s="7" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -1437,261 +1457,261 @@
     <row r="18" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="7" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="7" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
       <c r="B20" s="7" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="J21" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
       <c r="B22" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>140</v>
-      </c>
       <c r="E22" s="7" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
       <c r="B23" s="9" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H24" s="9"/>
       <c r="I24" s="9" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J24" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
       <c r="B25" s="7" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="7" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="7" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
